--- a/survey_templates/041_pet_product_packaging_preference_survey--survey_templates.xlsx
+++ b/survey_templates/041_pet_product_packaging_preference_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>very_important</t>
+          <t>very important</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>somewhat_important</t>
+          <t>somewhat important</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>not_very_important</t>
+          <t>not very important</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>not_at_all_important</t>
+          <t>not at all important</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>plant_based</t>
+          <t>plant based</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very low</t>
         </is>
       </c>
     </row>
